--- a/pds_admin_WB/Backend/Backend/Result_Sheet_leg3.xlsx
+++ b/pds_admin_WB/Backend/Backend/Result_Sheet_leg3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>Scenario</t>
   </si>
@@ -82,16 +82,10 @@
     <t>WestBengal</t>
   </si>
   <si>
-    <t>Purba Bardhaman</t>
-  </si>
-  <si>
     <t>Kolkata</t>
   </si>
   <si>
-    <t>EF14003</t>
-  </si>
-  <si>
-    <t>EBDNFM1</t>
+    <t>abx</t>
   </si>
   <si>
     <t>Xyz</t>
@@ -103,10 +97,10 @@
     <t>Wholesale</t>
   </si>
   <si>
-    <t>Def</t>
-  </si>
-  <si>
-    <t>Paschim Bardhaman</t>
+    <t>AJOY NATH YADAV</t>
+  </si>
+  <si>
+    <t>Alipurduar</t>
   </si>
   <si>
     <t>Wheat</t>
@@ -470,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -542,26 +536,26 @@
       <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2">
+        <v>611</v>
+      </c>
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
       <c r="G2">
-        <v>23.474314</v>
+        <v>22.521734</v>
       </c>
       <c r="H2">
-        <v>87.70725899999999</v>
+        <v>88.30223599999999</v>
       </c>
       <c r="I2" t="s">
         <v>20</v>
       </c>
       <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
         <v>25</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
       </c>
       <c r="L2" t="s">
         <v>21</v>
@@ -570,19 +564,19 @@
         <v>22</v>
       </c>
       <c r="N2">
-        <v>23.440923</v>
+        <v>22.521734</v>
       </c>
       <c r="O2">
-        <v>87.67574399999999</v>
+        <v>88.30223599999999</v>
       </c>
       <c r="P2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q2">
-        <v>748.64</v>
+        <v>21.2</v>
       </c>
       <c r="R2">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -599,22 +593,22 @@
         <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>23.474314</v>
+        <v>22.521734</v>
       </c>
       <c r="H3">
-        <v>87.70725899999999</v>
+        <v>88.30223599999999</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
       </c>
       <c r="K3" t="s">
         <v>27</v>
@@ -623,414 +617,22 @@
         <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>23.440923</v>
+        <v>22.573481</v>
       </c>
       <c r="O3">
-        <v>87.67574399999999</v>
+        <v>88.23092200000001</v>
       </c>
       <c r="P3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q3">
-        <v>748.64</v>
+        <v>20</v>
       </c>
       <c r="R3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4">
-        <v>611</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4">
-        <v>22.521734</v>
-      </c>
-      <c r="H4">
-        <v>88.30223599999999</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4">
-        <v>611</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" t="s">
-        <v>23</v>
-      </c>
-      <c r="N4">
-        <v>22.521734</v>
-      </c>
-      <c r="O4">
-        <v>88.30223599999999</v>
-      </c>
-      <c r="P4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4">
-        <v>391.48825</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5">
-        <v>611</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5">
-        <v>22.521734</v>
-      </c>
-      <c r="H5">
-        <v>88.30223599999999</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>611</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N5">
-        <v>22.521734</v>
-      </c>
-      <c r="O5">
-        <v>88.30223599999999</v>
-      </c>
-      <c r="P5" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q5">
-        <v>391.48825</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6">
-        <v>23.440923</v>
-      </c>
-      <c r="H6">
-        <v>87.67574399999999</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6">
-        <v>23.50248767</v>
-      </c>
-      <c r="O6">
-        <v>87.73095685</v>
-      </c>
-      <c r="P6" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q6">
-        <v>748.64</v>
-      </c>
-      <c r="R6">
-        <v>11.2945</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7">
-        <v>23.474314</v>
-      </c>
-      <c r="H7">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="I7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7">
-        <v>23.50248767</v>
-      </c>
-      <c r="O7">
-        <v>87.73095685</v>
-      </c>
-      <c r="P7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q7">
-        <v>46.26</v>
-      </c>
-      <c r="R7">
-        <v>5.3613</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8">
-        <v>23.474314</v>
-      </c>
-      <c r="H8">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="I8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N8">
-        <v>23.50248767</v>
-      </c>
-      <c r="O8">
-        <v>87.73095685</v>
-      </c>
-      <c r="P8" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q8">
-        <v>46.26</v>
-      </c>
-      <c r="R8">
-        <v>5.3613</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9">
-        <v>23.474314</v>
-      </c>
-      <c r="H9">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9">
-        <v>23.474314</v>
-      </c>
-      <c r="O9">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="P9" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q9">
-        <v>46.26</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10">
-        <v>23.474314</v>
-      </c>
-      <c r="H10">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10">
-        <v>23.474314</v>
-      </c>
-      <c r="O10">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="P10" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q10">
-        <v>46.26</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
+        <v>19.0827</v>
       </c>
     </row>
   </sheetData>
